--- a/data/trans_dic/P33B_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R2-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,23; 31,15</t>
+          <t>22,72; 29,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,53; 41,11</t>
+          <t>36,27; 41,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,78; 36,25</t>
+          <t>31,57; 35,99</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,23; 12,34</t>
+          <t>10,39; 13,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,24; 18,54</t>
+          <t>17,46; 20,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,74; 15,04</t>
+          <t>14,34; 16,43</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,97; 13,75</t>
+          <t>8,95; 14,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,93; 16,36</t>
+          <t>12,2; 16,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,9; 14,33</t>
+          <t>11,32; 14,59</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,14; 14,58</t>
+          <t>12,83; 15,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,35; 22,24</t>
+          <t>21,36; 23,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,73; 18,32</t>
+          <t>17,57; 19,31</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>141545</t>
+          <t>151764</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>289770</t>
+          <t>320393</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431316</t>
+          <t>472158</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>124780; 160419</t>
+          <t>131438; 171783</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>267610; 309652</t>
+          <t>297917; 340909</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>403000; 459713</t>
+          <t>441880; 503852</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>240284</t>
+          <t>260060</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>364897</t>
+          <t>413896</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>605181</t>
+          <t>673956</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>165619; 282451</t>
+          <t>231704; 292163</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>273854; 414961</t>
+          <t>379124; 445123</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>486439; 680855</t>
+          <t>631227; 723194</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71966</t>
+          <t>80897</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92501</t>
+          <t>104761</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>164467</t>
+          <t>185658</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>57974; 88908</t>
+          <t>63698; 100018</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>78800; 108049</t>
+          <t>89627; 121054</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>142431; 187302</t>
+          <t>163675; 211104</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>453796</t>
+          <t>492721</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>747169</t>
+          <t>839051</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1200964</t>
+          <t>1331771</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>350064; 503136</t>
+          <t>451731; 535370</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>597175; 811970</t>
+          <t>796096; 884285</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1046167; 1301110</t>
+          <t>1273355; 1399383</t>
         </is>
       </c>
     </row>
